--- a/StructureDefinition-ExtString.xlsx
+++ b/StructureDefinition-ExtString.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ExtString.xlsx
+++ b/StructureDefinition-ExtString.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
